--- a/通用/房屋说明-变电站.xlsx
+++ b/通用/房屋说明-变电站.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="19.1640625" customWidth="1" min="7" max="7"/>
@@ -463,6 +463,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>水单价</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>电单价</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,8 +787,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>电：1.5元/度；水：7元/度</t>
-        </is>
+          <t>电 1.5 元/度；水 7 元/吨（已落至字段列）</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">

--- a/通用/房屋说明-变电站.xlsx
+++ b/通用/房屋说明-变电站.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -33,10 +33,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,7 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE599"/>
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,10 +74,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,52 +447,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.1640625" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>房号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>是否在租</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>打通房</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>收款人</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>水单价</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>电单价</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>水保底度数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>101</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -488,8 +518,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>102</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -501,8 +533,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>103</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -514,8 +548,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>105</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -527,8 +563,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>201</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -540,8 +578,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>202</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -553,8 +593,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>203</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -566,8 +608,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>205</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -579,8 +623,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>206</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -592,8 +638,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>207</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -605,8 +653,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>208</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="B12" t="b">
         <v>1</v>
@@ -618,8 +668,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>301</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
       </c>
       <c r="B13" t="b">
         <v>1</v>
@@ -631,8 +683,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>302</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
       </c>
       <c r="B14" t="b">
         <v>1</v>
@@ -644,8 +698,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>303</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -657,8 +713,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>305</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -670,8 +728,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>306</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -683,8 +743,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>307</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
       </c>
       <c r="B18" t="b">
         <v>1</v>
@@ -696,8 +758,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>308</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
       </c>
       <c r="B19" t="b">
         <v>1</v>
@@ -709,8 +773,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>401</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
       <c r="B20" t="b">
         <v>1</v>
@@ -722,8 +788,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>402</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
       </c>
       <c r="B21" t="b">
         <v>1</v>
@@ -735,8 +803,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>405</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
       </c>
       <c r="B22" t="b">
         <v>1</v>
@@ -748,8 +818,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>406</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
       </c>
       <c r="B23" t="b">
         <v>1</v>
@@ -761,8 +833,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>407</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
       </c>
       <c r="B24" t="b">
         <v>1</v>
@@ -774,8 +848,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>408</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
       </c>
       <c r="B25" t="b">
         <v>1</v>
@@ -783,11 +859,6 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>张</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>电 1.5 元/度；水 7 元/吨（已落至字段列）</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -798,8 +869,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>501</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
       </c>
       <c r="B26" t="b">
         <v>1</v>
@@ -811,8 +884,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>502</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
       </c>
       <c r="B27" t="b">
         <v>1</v>
@@ -824,8 +899,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>505</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
       </c>
       <c r="B28" t="b">
         <v>1</v>
@@ -837,8 +914,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>506</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
       </c>
       <c r="B29" t="b">
         <v>1</v>
@@ -850,8 +929,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>507</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
       </c>
       <c r="B30" t="b">
         <v>1</v>
@@ -863,8 +944,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>508</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
       </c>
       <c r="B31" t="b">
         <v>1</v>
@@ -876,8 +959,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>601</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
       </c>
       <c r="B32" t="b">
         <v>1</v>
@@ -889,8 +974,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>602</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
       </c>
       <c r="B33" t="b">
         <v>1</v>
@@ -902,8 +989,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>605</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
       </c>
       <c r="B34" t="b">
         <v>1</v>
@@ -915,8 +1004,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>606</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -928,8 +1019,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>607</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
       </c>
       <c r="B36" t="b">
         <v>1</v>
@@ -941,8 +1034,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>608</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
       </c>
       <c r="B37" t="b">
         <v>1</v>
@@ -965,14 +1060,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
+    <col width="8" customWidth="1" min="4" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1792,7 +1884,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>初始基准（电：1.5元/度；水：7元/度）</t>
+          <t>初始基准</t>
         </is>
       </c>
     </row>

--- a/通用/房屋说明-变电站.xlsx
+++ b/通用/房屋说明-变电站.xlsx
@@ -646,16 +646,11 @@
         </is>
       </c>
       <c r="B11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>张</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>已退房（2026-08 结算后不再出收据）</t>
         </is>
       </c>
     </row>
@@ -688,11 +683,6 @@
           <t>张</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>新租客：宋泽友（2026-09 起，房租780，无管理费，租期16日-次月16日，保留水保底1吨）</t>
-        </is>
-      </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -804,11 +794,6 @@
           <t>张</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>新租客：余金华（2026-09 起，房租750，租期16日-次月16日）</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,16 +847,11 @@
         </is>
       </c>
       <c r="B24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>张</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>已退房（2026-08 结算后不再出收据）</t>
         </is>
       </c>
     </row>
@@ -986,11 +966,6 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>张</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>换租客：胡林艳（2026-09 起，房租700，租期1日-30日）</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2440,6 +2415,138 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>钟建华</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>650</v>
+      </c>
+      <c r="E42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>13日-次月13日</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>新租客（10月13日起租）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>邓先凯</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>650</v>
+      </c>
+      <c r="E43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2日-次月2日</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>新租客（10月2日起租）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>张永刚</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>900</v>
+      </c>
+      <c r="E44" t="n">
+        <v>30</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1日-30日</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>换租客+涨租（林成为850→张永刚900，管理费0→30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>林成为</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>900</v>
+      </c>
+      <c r="E45" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1日-30日</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>换租客（羊晓静→林成为）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
